--- a/仕事/AIを活用したまちづくり事例集.xlsx
+++ b/仕事/AIを活用したまちづくり事例集.xlsx
@@ -10,7 +10,7 @@
     <sheet name="AIまちづくり事例" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AIまちづくり事例'!$A$1:$H$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AIまちづくり事例'!$A$1:$H$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00808080"/>
+        <bgColor rgb="00808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,11 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -454,20 +464,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>項番</t>
@@ -509,608 +519,4040 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>■ 国内事例（70件）</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>AIを活用したまちづくり 市民参加型実証実験（大阪・京橋）</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>京橋駅周辺エリアにおいて、まちの分析・可視化・未来予測プラットフォーム「みんなのまちAI」と、まちづくり参加アプリ「みんスマ」を活用。センサーレスでの街のデジタル化・分析と、住民がまちづくりに参加しやすくなる仕組みづくりの2テーマで実証を実施。</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>NTT西日本、京阪ホールディングス、NTT、NTTデータ</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>2023年度（2023年1月〜3月）</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>多数のセンサー設置に頼らずAIで人流等を可視化・将来予測する低コスト手法と、スマホアプリによる住民参加の仕組みを組み合わせた点が特徴。</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>https://www.ntt-west.co.jp/news/2301/230123a.html</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>対象エリア：大阪市 京橋駅周辺</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="90" customHeight="1">
-      <c r="A3" s="2" t="n">
+    <row r="4" ht="85" customHeight="1">
+      <c r="A4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>「みんなのまちAI®」による未来のまちづくり支援業務</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>人流・建物・地図・オープンデータ等の都市データをデジタル上に再現・可視化するツールを用い、商業施設や道路整備による人流変化のシミュレーションを行い、自治体等の都市計画・観光促進の施策検討を支援するコンサルティング業務。</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>NTTビジネスソリューションズ、NTT西日本</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2024年度（2024年4月〜）</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>都市シミュレーション機能により開発後の人流変化を事前予測でき、データ分析からコンサルティングまで一気通貫で提供する点が特徴。</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>https://www.nttbizsol.jp/newsrelease/202404041000001021.html</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>サービス名：みんなのまちAI®</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="2" t="n">
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>生成AIを使ったまちづくりワークショップ（公共空間×生成AI）</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>特定エリアに特化した画像生成AIを住民参加型ワークショップに導入し、新たなキーワードを反映したエリアの将来像を可視化。まちづくりの合意形成プロセスにおける将来像共有ツールとして活用。</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>公共R不動産、NESS</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2023年度頃</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>エリア特化型の画像生成AIにより「地域らしさ」を保ちながら将来像を視覚化し、住民との合意形成を支援する点が特徴。</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>https://www.realpublicestate.jp/post/r_ai-02/</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>各地でのワークショップ展開を想定した実証的取り組み</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1">
-      <c r="A5" s="2" t="n">
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>画像生成AIによるボトムアップ型まちづくりデザイン（墨田区京島）</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>地域住民へのフィールドワークで「京島らしさ」を表す画像を収集し、Stable Diffusionに追加学習させることで地域特性を非言語要素として抽出。多数の画像を生成し、京島の伝統的風景を活かした共有農場等のまちづくり提案を作成。</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>東京大学（大学院生・研究グループ）</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>2024年度頃</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>地域らしさという言語化しにくい要素をAIに学習させ、住民の一般意志を反映したボトムアップ型のデザイン提案を大量生成する点が特徴。</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>https://shinkenchiku.online/column/8172/</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>対象エリア：東京都墨田区京島</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1">
-      <c r="A6" s="2" t="n">
+    <row r="7" ht="85" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>スマートシティ会津若松「都市OS」</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>自治体の既存システムを代替せず、複数分野に共通するニーズに応える基盤「都市OS」を開発。オプトイン方式のデータ活用と市民中心のICTを掲げ、食農・観光・防災・ヘルスケア・行政・決済等22サービスと連携。RPAやAIを活用した業務改革も推進。</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>会津若松市、アクセンチュア等</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>2011年度〜（継続中）</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>住民の事前同意（オプトイン）に基づくデータ活用と、他自治体へも横展開可能な共通基盤である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>https://robotstart.info/2023/03/20/aizu-aict-city-os.html</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>都市OSは全国複数都市に展開</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="85" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>柏の葉スマートシティ AIカメラによる人流分析・異常検知</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>柏の葉キャンパス駅周辺に国内最大規模となるエッジAIカメラ29台を設置し、AIによるリアルタイム画像分析で異常行動（転倒、うずくまり、凶器所持等）や不審な立ち入りの検知、歩行者の人流解析を実施。個人が特定できない形にデータを加工しプライバシーに配慮。</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>三井不動産、クリューシステムズ、UDCKタウンマネジメント</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>2021年度〜</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>カメラ側で解析を完結するエッジAIにより、プライバシーに配慮しつつリアルタイムでの安心・安全なタウンマネジメントを実現する点が特徴。</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mitsuifudosan.co.jp/corporate/news/2021/0921/</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>対象エリア：千葉県柏市 柏の葉キャンパス駅周辺</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="85" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>加古川市 AI搭載高度化見守りカメラ</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>市内約150カ所（累計約1,560台）にAI機能搭載の見守りカメラを設置。悲鳴等の異常音を検知し警告するI型と、危険運転検知・交通量や人流データの自動把握も行うII型を配備し、犯罪・交通事故の未然防止を図る。</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>加古川市</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>2016年度〜（順次拡大、2023年度にAI高度化）</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>AIによる異常音・危険運転の自動検知と通報を組み合わせ、設置から約6年間で刑法犯認知件数が約4割減少する効果を上げた点が特徴。</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>https://kakogawa.keizai.biz/headline/2510</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2025年4月からは市民参加型「みまもりアプリ」も開始</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="85" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>つくばスーパーサイエンスシティ構想（オンデマンド型移動期日前投票所）</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>有権者がスマートフォンや電話で予約した日時に投票箱搭載車両が自宅前まで来訪するオンデマンド型移動期日前投票所の模擬実証を実施。立会人の役割の一部をロボットによる遠隔立会で代替する検証も実施。</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>つくば市、KDDI、スパイラル、東京海上日動</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>2023年度（2024年1月実証）</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>AI・ロボティクスとオンデマンド配車の組み合わせにより、移動困難者の投票参加を支援するまちづくり・行政DXの取り組みである点が特徴。</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>https://www.spiral-platform.co.jp/20240115/1479/</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>2024年秋の市長・市議選での一部実用化を目指す</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="85" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>AIオンデマンドバス「のるーと」</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>既存の地域振興バス路線を段階的にAIオンデマンド型のデマンド交通へ転換。利用者の予約に応じてAIが効率的な運行ルートをその都度生成し、過疎化・高齢化地域における移動手段を確保。</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>塩尻市（長野県）</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>2021年度〜</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>全国有数の成功事例とされ、路線バスからAIオンデマンド交通への段階的な転換モデルを確立した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>https://book.st-hakky.com/industry/ai-ondemand-transportation-innovation</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>同種の取り組みは玉野市（岡山県）、桑名市（三重県）、北本市（埼玉県）等でも展開</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="85" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>渋谷区生成AIチャットボット</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>GPT-4o相当のモデルとRAG技術を組み合わせ、行政サービスの手続きや制度に関する住民からの問い合わせに自動で回答する生成AIチャットボットサービスを提供。ポータルサイトやLINEから利用可能。</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>渋谷区</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>2025年度（2025年3月開始）</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>住民参加によるチューニング募集の仕組みを持つ「共創型AI」であり、開始2カ月で10万件超のQ&amp;A対応・解決率77%を達成した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.shibuya.tokyo.jp/kusei/kocho/ai-chatbot/ai_chatbot.html</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>多言語対応・画像アップロード機能あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="85" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>仙台市新庁舎建替・東北大学青葉山新キャンパスにおけるAI活用実証</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>総務省「地域社会DX推進パッケージ事業（AI検証タイプ）」の一環として、建替工事現場においてAIを活用した実証実験を開始。7社によるコンソーシアムで現場業務の効率化・高度化を検証。</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>NTTドコモビジネス（代表）ほか7社コンソーシアム、仙台市、東北大学</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2025年度（2025年12月開始）</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>都市インフラ整備（庁舎・キャンパス建設）の現場そのものにAIを実装し、まちづくりの基盤整備プロセス自体を効率化する点が特徴。</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ntt.com/about-us/area-info/article/20251205.html</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>総務省補正予算事業を活用</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="85" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市 AI型教材「Qubena」による個別最適化学習</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市が市内小中学校にAI型教材「Qubena」を導入し、児童生徒の学習ログ・習熟度・解答傾向をAIが解析してつまずきの原因を特定、一人ひとりに最適な問題を自動で出題する仕組みを構築した。</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>東大阪市（教育委員会）、株式会社COMPASS</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>2020年度〜（全校導入）</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>利用頻度の高い児童ほど学力テストで明確な学力向上が見られたと報告されており、教育分野での自治体全体でのAI個別最適化学習の代表事例である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.edutechnology.co.jp/service/aikyouiku-support/ai-cases-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>同様の取り組みは奈良市「学びなら」等でも展開</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="85" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>福岡市地下鉄 AI防犯カメラ不審行動検知実証</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>福岡市交通局は2024年9月から地下鉄空港線博多駅のホームとコンコースに計10台の防犯カメラを設置し、画像解析AIによる実証実験を開始した。AIが人物の動きを解析し「転倒」「ふらつき」「喧嘩・暴力」「車椅子」「白杖」「うずくまり等の違和感」の6種類を自動検知してキーワード表示する。駅長事務室のモニターで係員が映像とともに確認し、必要に応じて現場に急行する体制を構築した。</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>福岡市交通局</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>1日約7万人が利用する主要駅の実際の運行環境下で、複数の異常行動パターンを同時にリアルタイム検知する点が特徴。</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nikkei.com/article/DGXZQOJC04A2K0U4A900C2000000/</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="85" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>枚方市 AI警備システムによる公園見守り実証</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>大阪府枚方市は株式会社アジラと連携し、次世代AI警備システム「AI Security asilla」を市内公園に導入する社会実証を2023年10月13日から11月26日まで実施した。既存の防犯カメラ映像をAIが解析し、異常行動や不審行動を検知した際にのみ瞬時に映像を通知する仕組み。転倒やふらつき、急病人などの見守りに加え、迷惑行為や不審者の早期発見、イベント時の人流計測も行った。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>大阪府枚方市、株式会社アジラ</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>2023年</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>24時間365日の常時監視ではなく異常検知時のみ通知する「必要なときだけ介入」型の運用で、警備負担を抑えつつ公共空間の安全性向上とスマートシティ化を両立させた点。</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000200.000043312.html</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="85" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>岐阜県 AIクラウド河川監視・水位予測実証実験</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>NTT西日本岐阜支店、NTTPCコミュニケーションズ、構造計画研究所の3者は、電柱に設置した河川カメラの画像をAIで解析して水位を計測し、さらに数理工学技術で中小河川の水位を予測するクラウドサービスの実証実験を実施した。第1期は岐阜県内4河川、第2期は岐阜県を含む全国5エリア10河川に拡大して検証した。</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>NTT西日本岐阜支店、NTTPCコミュニケーションズ、構造計画研究所</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2020年〜2022年</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>河川専用の水位計を新設せず、既存インフラの電柱にカメラを設置する低コスト手法で、中小河川の水位監視網を全国に展開できる可能性を示した点。</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nttpc.co.jp/press/2022/02/202202241500.html</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>通称「仮想水位計」と呼ばれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="85" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>富山県 ハイブリッドAI縦断水位予測システム実証</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ハイドロ総合技術研究所は、富山県のDX推進事業「Digi-PoC TOYAMA」の枠組みで、予測降雨や河川水位・流量の観測情報をもとに河川全体の縦断的な水位を予測する「ハイブリッドAI縦断水位予測システム」の実証実験を実施した。あわせてカメラ映像から流速・流量を非接触で計測する「Hydro-STIV」も導入した。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ハイドロ総合技術研究所（富山県Digi-PoC TOYAMA事業）</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>記載なし（近年）</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>単一地点の水位予測にとどまらず河川全体を縦断的に予測するモデルであることに加え、非接触計測技術により出水時の観測員の安全確保にも寄与する点。</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>https://digi-poc-toyama.jp/topics/post-1464/</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>大垣市 避難所受付支援・混雑可視化実証実験</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>岐阜県大垣市はGcomホールディングスおよび株式会社バカンと2021年11月に実証実験に関する連携協定を締結し、安井地区をモデル地区として防災訓練を実施した。スマートフォンでの事前登録による非接触の避難所受付と、避難所ごとの混雑状況を地図上にリアルタイム表示するサービス「VACAN Maps」を組み合わせ、避難所受付時間を最大80%短縮できることを確認した。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>岐阜県大垣市、Gcomホールディングス株式会社、株式会社バカン</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2021年</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>避難者の受付という「入口」の混雑緩和と、避難所選択の判断材料となる混雑可視化を同時に解決する点で、他の防災DX施策と一線を画す。</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.ogaki.lg.jp/0000055638.html</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>茨城県 ドローン×AI河川堤防診断システム</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>茨城県は、河川堤防等の被災状況を迅速に把握するため、ドローンの自動航行機能とAIによる画像解析を組み合わせた診断システムを導入した。撮影画像から堤防の変状箇所をAIが自動検出し、大規模出水後の被災箇所把握に要していた期間を従来の7日程度から3日程度へと大幅に短縮した。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>茨城県</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>記載なし</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>目視による人手中心の巡視をドローンの自動飛行とAI画像解析に置き換えることで、大規模災害時の初動調査を高速化した点。</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.soumu.go.jp/denshijiti/digital_transformation_portal/case/r07_dx3_42.html</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="85" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>熊本市 AI防災・減災システム導入（洪水・地震予測）</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>熊本市は損害保険ジャパン日本興亜、米シリコンバレー発の防災スタートアップOne Concern、ウェザーニューズと連携し、日本の自治体として初めてAIを活用した防災・減災システムを導入した。気象・人口・インフラ・河川水位・地震検知などのデータをAIで解析して洪水・地震の被害をリアルタイムに予測する仕組みを構築した。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>熊本市、損害保険ジャパン日本興亜、One Concern、ウェザーニューズ</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>2019年</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>洪水と地震という複数の災害種別を同一プラットフォームでリアルタイムに被害予測する点、および海外の防災AIベンチャーの技術を日本で初めて自治体導入した点。</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>https://jp.weathernews.com/news/27902/</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="85" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>川崎市 富岳AI津波浸水予測・避難実証実験</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>理化学研究所計算科学研究センターは東北大学災害科学国際研究所、東京大学地震研究所、富士通、川崎市と共同で、スーパーコンピュータ「富岳」による津波シミュレーションをもとにAIで高解像度かつリアルタイムの浸水予測データを生成し、それを活用した地域コミュニティ型の避難実証実験を2022年3月に川崎市で実施した。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>理化学研究所計算科学研究センター、東北大学災害科学国際研究所、東京大学地震研究所、富士通、川崎市</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>2022年</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>スーパーコンピュータ「富岳」の計算資源とAIを組み合わせ、津波発生後に住民が実際の避難行動に活用できる速さで浸水予測を提供する点。</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>https://www.r-ccs.riken.jp/outreach/topics/20220303-1/</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="85" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>裾野市 AI搭載スマート道路灯による見守り実証</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>静岡県裾野市とNTTコミュニケーションズは、AI搭載スマート道路灯とローカル5Gを活用し、速度超過車両の検知や歩行者の車道侵入検知などを行う実証実験を実施した。AI解析と連動した運転手・歩行者への注意喚起に加え、高画質映像を用いた保護者等による通学路の遠隔見守りも検証した。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>静岡県裾野市、NTTコミュニケーションズ株式会社</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>2023年度</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>防犯カメラ単体ではなく道路灯にAI・5G・センサーを統合し、交通安全と子どもの通学路見守りを同時に実現する複合型インフラである点。</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.ntt.com/about-us/press-releases/news/article/2023/1005.html</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="85" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>さいたま市 AI感染症流行予測サービス</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>さいたま市は株式会社日立製作所と連携し、日本医師会ORCA管理機構の罹患者数統計データと日立のAI・機械学習技術を組み合わせた「感染症予報サービス」の社会実装に取り組んだ。インフルエンザ等の感染症の流行状況をAIが予測し、市の情報媒体を通じて住民に流行予報や予防情報を配信することで、行動変容を促すことを目的とした。</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>さいたま市、株式会社日立製作所</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2021年度〜2022年度（全国展開）</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>防犯・防災分野が中心のAIまちづくり事例の中で、感染症という公衆衛生分野にAI予測を応用し、市単独の取り組みから県・全国へ横展開した点。</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>https://www.chisou.go.jp/tiiki/kinmirai/pdf/2104_saitama_torimatome.pdf</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="85" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>茨城県境町 自動運転バス社会実装</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>境町は2020年11月から自治体として国内で初めて自動運転バスを定常運行として導入し、通学・通院等の生活路線として日常的に走行させている。2023年にはエストニアAuve Tech社製の自動運転車両「MiCa」の導入を決定し、特定条件下で完全自動運転となる「レベル4」化に向けた実証を継続中。</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>茨城県境町、BOLDLY株式会社（ソフトバンク子会社）</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2020年〜継続中（2023年にMiCa導入決定）</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>実証実験にとどまらず、自治体自らが定常運行の交通インフラとして自動運転バスを導入し、住民の生活の足として恒常的に利用されている点が他の実証事例と一線を画す。</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>https://www.town.ibaraki-sakai.lg.jp/page/page002440.html</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="85" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>岡山市 AI渋滞予測信号制御実証</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>NEDOと岡山県警察は、岡山市内の交差点においてAIによる渋滞予測を活用した信号制御の実証実験を実施した。AIが交通量データから将来の渋滞長を予測し信号制御に反映する仕組みで、既存の車両検知センサ数を半減しても渋滞状況に変化がなく信号制御性能を維持できることを確認した。</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>国立研究開発法人新エネルギー・産業技術総合開発機構（NEDO）、岡山県警察</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2021年度</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>渋滞緩和効果だけでなく、センサー台数削減による交通管制システムの低コスト化効果まで定量的に実証した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nedo.go.jp/news/press/AA5_101538.html</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="85" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>タクシー配車アプリ「GO」のAI予約</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>タクシー配車アプリ「GO」で提供される「AI予約」機能は、AIがエリアごとの利用トレンドをリアルタイムに予測し、利用者に代わって空車タクシーを自動的に探して手配する。従来の「希望の日時に呼ぶ」機能をAI技術でリニューアルし、需給予測により配車成立率を大幅に高めている。</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>GO株式会社</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2023年〜</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>実証実験ではなく、東京・大阪など全国主要都市で商用サービスとして日常的に稼働しているAIタクシー配車の代表例である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>https://go.goinc.jp/service/ai-reservation</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="85" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>ヤマト運輸×アルフレッサ AI共同配送</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>ヤマト運輸はアルフレッサとの協業により、ビッグデータとAIを用いてヘルスケア商品（医薬品等）の配送業務量を予測し、適正な配車計画を自動立案するシステムを導入した。異業種間の共同配送スキーム構築における車両手配・要員配置の効率化を実現した。</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>ヤマトホールディングス株式会社、アルフレッサ株式会社</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>2021年</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>単純な配送ルート最適化ではなく、卸売業との共同配送という業種横断の物流再編にAI需要予測を組み込んだ点が特徴。</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>https://www.yamato-hd.co.jp/news/2021/newsrelease_20210803_1.html</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="85" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>NEC 機械式駐車場AI入出庫判定実証</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>NECは横浜市内のオフィスビルに併設された機械式駐車場において、カメラとAIを組み合わせ、車種・年式・車両寸法・ルーフキャリアなどの付属品を認識し、入庫可否を自動判定する実証実験を実施した。</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>日本電気株式会社（NEC）</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2026年1月〜</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>従来は係員が目視で行っていた機械式駐車場特有の入庫可否判断を、AI画像認識によって代替しようとする点が他の駐車場AI事例と異なる。</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>https://www.itmedia.co.jp/news/articles/2512/01/news070.html</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="85" customHeight="1">
+      <c r="A30" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>日本郵便 ドローン配送レベル4飛行実証</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>日本郵便はACSL製の国産ドローン「PF2-CAT3」を用い、東京都奥多摩町において操縦者が目視できない有人地帯上空を飛行する「レベル4」でのドローン配送を国内で初めて実施した。奥多摩郵便局から約2km先の配送先まで約1kgの荷物を約5分で届けることに成功した。</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>日本郵便株式会社、株式会社ACSL</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>2023年3月</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>国内初のレベル4飛行によるドローン配送実証であり、中山間地域における郵便・物流網維持を見据えている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lnews.jp/2023/03/p0317408.html</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="85" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>NEXCO中日本×ドコモ AI渋滞予測（東名高速）</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>NEXCO中日本とNTTドコモは、東名高速道路の御殿場JCT〜東京IC間上り線を対象に、ドコモの携帯電話網から得られる人口統計データとNEXCO中日本の過去の交通データを組み合わせたAIによる渋滞予測の実証実験を実施した。</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>中日本高速道路株式会社（NEXCO中日本）、株式会社NTTドコモ</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>2021年10月〜</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>都市内の信号制御ではなく高速道路の広域交通流を対象とし、携帯電話の人流ビッグデータを渋滞予測に活用している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>https://k-tai.watch.impress.co.jp/docs/news/1359277.html</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="85" customHeight="1">
+      <c r="A32" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>高萩市「MyRideのるる」AIオンデマンドバス</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>茨城県高萩市では、みちのりホールディングス子会社の茨城交通が、米Via Transportation社の技術を用いたAIオンデマンドバス「MyRideのるる」を導入した。利用者がスマホや電話でリクエストすると、AIが乗車人数・出発地・目的地・道路混雑状況から最適経路をリアルタイムに算出し、既存の定時定路線バスと組み合わせて運行する。</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>茨城県高萩市、茨城交通株式会社（みちのりホールディングス）</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>2021年7月実証開始、2022年10月本格運行開始</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>米国発のダイナミックルーティング技術を採用し、定時定路線バスとオンデマンド車両を組み合わせたハイブリッド型の地域交通再編である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>https://project.nikkeibp.co.jp/atclppp/PPP/434167/090200221/</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="85" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>JR東日本×日立 鉄道運行管理AI</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>JR東日本と日立製作所は、山手線をはじめとする首都圏在来線の運行管理システムにAIを活用した「復旧対応支援AI」を2023年4月から本格運用し、設備故障発生時の原因特定や復旧方法の提示を自動化して復旧時間の大幅短縮を実現した。2025年には信号通信設備向けに生成AIエージェントを活用したさらなる高度化の共同検証を開始している。</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>東日本旅客鉄道株式会社（JR東日本）、株式会社日立製作所</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>2023年本格運用開始、2025年生成AI活用の共同検証開始</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>ベテラン指令員の経験知をAIに学習させた上で、鉄道の安全運行業務に段階的に生成AIまで導入範囲を拡大している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jreast.co.jp/press/2025/20250610_ho02.pdf</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="85" customHeight="1">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>静岡型MaaS「AI相乗りタクシー」実証</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>静岡市を中心とした「静岡型MaaS基幹事業実証プロジェクト」において、AIを活用した相乗りタクシーサービスの実証実験が実施された。複数の利用者からの配車リクエストをAIがリアルタイムに解析し、効率的な相乗り経路・配車を行うことで、公共交通の利便性向上とMaaSシステムに対する市民の受容性を検証した。</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>静岡市、株式会社未来シェア、静岡型MaaS推進協議会参画企業</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>2019年11月</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>単独のオンデマンド交通実証ではなく、複数モビリティサービスを統合するMaaS基幹事業の一環としてAI相乗りタクシーを位置づけている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>https://www.miraishare.co.jp/201911shizuokamaas/</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="85" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Woven City「AI Vision Engine」による安全都市実証</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>トヨタとWoven by Toyotaは静岡県裾野市の実証都市「Woven City」で、街中のカメラ映像をリアルタイムに言語化・理解する独自の視覚言語モデル（VLM）「Woven City AI Vision Engine」を開発した。信号機・カメラ・車両・歩行者のデータを統合し、事故が起きる前にリスクを検知・予測して街全体で共有する仕組みを構築。実際に住む約100人の住民の生活データを学習に活用している。</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>トヨタ自動車／Woven by Toyota（静岡県裾野市）</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>2025年（Phase1竣工・入居開始）〜2026年4月（AI Vision Engine発表）</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>実在の住民が暮らす「生きた実証都市」で、AIが街全体の映像を理解し事故予防に活用する点が特徴。仮想空間（デジタルツイン）と実際の街での実証を高速に循環させる開発体制を持つ。</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>https://jidounten-lab.com/u_toyota_wovencity_ai</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>MVBench（動画理解AIの評価指標）で世界トップ水準の性能とされる</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="85" customHeight="1">
+      <c r="A36" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>衛星画像×AI×PLATEAUによる災害・減災シミュレーション</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>宇宙ベンチャーの株式会社スペースシフトは、国交省PLATEAUの3D都市モデルと衛星（光学・SAR）画像をAIで解析する技術を組み合わせ、発災前後の変化検知や建物被害推定を迅速に行うシミュレーションを開発した。機械学習で建物の屋根形状・色を自動推定し、現地調査なしで都市情報を再現する。この取り組みはPLATEAU AWARD 2024で表彰された。</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>株式会社スペースシフト（国土交通省PLATEAUプロジェクト、WHERE社と共同実証）</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>2024年（PLATEAU AWARD 2024受賞）</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>衛星データという広域・非接触の情報源とAI画像解析、3D都市モデルを組み合わせ、被災自治体への迅速な状況把握・無償データ提供を目指す点が特徴。</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mlit.go.jp/plateau/file/events/doc/2025_3-4_SS.pdf</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>PLATEAU Use Case「衛星データによる都市デジタルツインの構築調査業務」も参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="85" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>大成建設「AI設計部長」による概略設計自動生成</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>大成建設は、敷地条件や希望条件を入力するだけでAIが建築基準を考慮した複数の概略設計パターンを自動生成し、Revit形式で出力できる設計支援システム「AI設計部長」を開発した。あわせて画像生成AIを用いた建築デザイン支援システムも開発し、スケッチや模型の写真から専門ソフトの習熟なしに高精細な建築パースを生成できるようにした。</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>大成建設株式会社</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>2024年4月（AI設計部長発表）、2025年（画像生成AI建築デザイン支援システム発表）</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>都市計画・敷地条件から建築可能な規模・形状を即座に複数パターン提示する点、および画像生成AIで非専門家でも建築パースを作れる点が他の設計AI事例と異なる。</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>https://built.itmedia.co.jp/bt/articles/2404/16/news122.html</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="85" customHeight="1">
+      <c r="A38" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>森ビル「ヒルズネットワーク」都市OSによるまちの最適化</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>森ビルは六本木ヒルズ・虎ノ門ヒルズ・表参道ヒルズなど複数の「ヒルズ」を横断する共通ID「ヒルズID」を基盤に、来街者・テナントの行動データを統合するデジタルプラットフォーム「ヒルズネットワーク」を構築した。データ分析により顧客の解像度を高め、街の情報・クーポン・サービスを個人に合わせて最適化するパーソナライズを実現している。虎ノ門エリアではPLATEAUの3D都市モデルとビルのBIMデータを統合したデジタルツインの活用検証も行った。</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>森ビル株式会社（NEC、AWS等と技術連携）</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>2021年4月（サービス開始）、2023年度（PLATEAU×BIM検証）</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>単一の再開発地区ではなく複数の「ヒルズ」を横断してデータとIDを統合し、都市全体をパーソナライズ最適化の対象とする点が特徴。</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mori.co.jp/press/release/post_590/</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="85" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>GovTech東京「ブロードリスニング」による都市戦略への意見集約</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>東京都は2050年代の東京像を描く長期戦略「シン東京2050（仮称）」の策定にあたり、X（旧Twitter）の投稿やGoogleフォーム、郵送等で寄せられた膨大な数の住民意見をAIで分析・可視化する「ブロードリスニング」という手法を導入した。GovTech東京がオープンソースの意見分析ツールと生成AIを組み合わせて内製開発し、使用したプロンプトも公開して分析の透明性を確保した。</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>東京都（政策企画局）、GovTech東京</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>2024年11月〜12月</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>通常のパブリックコメントでは扱いきれない規模の意見をAIで構造化・可視化し、分析に使ったプロンプトまで公開する透明性を重視した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>https://note.govtechtokyo.jp/n/ndcf8d6b35939</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="85" customHeight="1">
+      <c r="A40" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>横浜市「Surfvote」による区別まちづくり意見募集</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>横浜市はPolimill社が運営するデジタル意見募集プラットフォーム「Surfvote」を活用し、市内18区それぞれの地域課題や将来像について、全市民を対象に意見・アイデアを募集する取り組みを開始した。オンライン上で誰でも論点を読み、選択肢への投票やコメントで意見を発信でき、区役所の施策検討の参考資料として活用している。</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>横浜市、Polimill株式会社</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>2024年7月開設〜継続実施</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>単発のパブリックコメントではなく通年・全区展開のプラットフォームとして、住民が「まち」単位で意見を出し合意形成に参加できる仕組みにしている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.yokohama.lg.jp/city-info/koho-kocho/press/shimin/2024/0711yokohamasurfvote.html</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="85" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>前橋市「都市OS」とまえばしIDによるデータ連携基盤</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>前橋市はスマートシティの技術的根幹となるデータ連携基盤（都市OS）を構築し、異なる分野・サービスのデータを円滑に連携・流通させる仕組みを整備した。あわせて個人情報を保護しつつ官民の各種サービスを利用できる独自ID「まえばしID」を全国に先駆けて導入し、都市OSを基盤に交通・防災・福祉など10のサービスを展開。「前橋市デジタルツイン」もオープンデータとして公開している。</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>前橋市（民間企業8社と設立した新会社が運営に関与）</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>2022年〜継続中</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>都市OSとまちのID基盤（まえばしID）を組み合わせ、官民サービスを住民一人ひとりに紐づけて提供する点、および3D都市データをオープンデータとして公開する点が特徴。</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.maebashi.gunma.jp/soshiki/toshikeikakubu/toshikeikaku/oshirase/47439.html</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="85" customHeight="1">
+      <c r="A42" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>東京都デジタルツイン「地下空間含む混雑可視化」実証</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>東京都は「東京都デジタルツイン実現プロジェクト」の一環として、大手町・丸の内・有楽町地区を対象に地上・地下通路のリアルタイムな人流・混雑情報を統合して可視化する技術実証を実施した。予測アルゴリズムやIoTセンサーで取得した混雑度データを基に、混雑を回避しながら安全に移動できる経路を案内するWebアプリを公開し、都民参加による検証を行った。</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>東京都（デジタルサービス局）、株式会社unerry等</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>2021年度</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>地上だけでなく地下空間も含めた三次元的な人流可視化・経路案内を都が主体となって実証した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>https://info.tokyo-digitaltwin.metro.tokyo.lg.jp/zissyou01/</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="85" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>竹中工務店「ゲームAI×BIM人流シミュレーション」</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>竹中工務店は、ゲーム内キャラクターが周囲を知覚・思考して行動する「ゲームAI」の技術と、同社が蓄積してきた人流計測データを組み合わせ、建物完成後に人がどのように動き、施設がどう使われるかを現実に近い形で再現する「人流シミュレーションシステム」を開発した。BIMデータと連動させ、建築計画や什器配置計画の検討段階から利用者の動線・混雑を予測できるようにした。</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>株式会社竹中工務店</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>2023年12月</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>実測の人流データで学習させたゲームAIにより、静的な統計データではなく個々の「人」が自律的に動くシミュレーションを実現している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.takenaka.co.jp/news/2023/12/01/pdf/20231207_Release_jinryu.pdf</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="85" customHeight="1">
+      <c r="A44" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>衛星画像×生成AIによる固定資産税課税調査（善通寺市）</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>香川県善通寺市の税務課職員が、対話型生成AI「ChatGPT」を使ってプログラムを自作し、毎年更新される衛星写真を比較分析するシステムを開発した。市内約7万筆の土地について、田畑が駐車場に変わるなど用途変化をAIが自動検出し、固定資産税の適正課税に活用する。</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>香川県善通寺市（税務課）</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>2024年度</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>外部委託なら約3,000万円かかる開発費を、職員が生成AIを活用して自作することで約120万円（約30分の1）に圧縮した内製開発モデル。</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>https://news.ksb.co.jp/article/15517617</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>開発は税務課の20〜40代若手職員約5人のチームが約1カ月で完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="85" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>AIによる保育所入所マッチングシステム（さいたま市）</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>さいたま市が富士通研究所・九州大学と共同で、保育所入所選考を最適化するAIマッチング技術を開発した。従来は職員が数日かけて行っていた約8,000人分の入所希望者の割り当てを、優先順位や兄弟同時入所などの条件を踏まえてわずか数秒で算出できるようにした。</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>さいたま市、富士通研究所、九州大学</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>2017年度</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>人手による選考結果とほぼ100%一致する精度を実現し、全国の自治体AI保育所マッチングの先駆け的事例となった。</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>https://www.itmedia.co.jp/enterprise/articles/1708/31/news070.html</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="85" customHeight="1">
+      <c r="A46" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>AI-OCRによる手書き申請書デジタル化実証（福岡市）</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>福岡市がNTTデータ・NTTデータ九州と共同で、就学援助申請書や給与支払報告書など11種類・計73帳票の手書きサンプルを用いてAI-OCRの読み取り精度を検証した。文字単位で平均93.3%、項目単位で平均88.57%の正読率を達成し、手書き文書デジタル化の実用可能性を確認した。</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>福岡市、NTTデータ、NTTデータ九州</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>2018年度</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>単一帳票でなく複数種類・大量サンプルで精度を横断検証し、他自治体への展開を見据えた実証実験とした点。</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>https://www.nttdata-kyushu.co.jp/information/2018/20181206-361.html</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="85" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>AI-OCRによるタクシー券事務の自動化（大子町）</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>茨城県大子町が、65歳以上高齢者向けタクシー運賃助成事業で使用する手書きのタクシー券（月平均約1,100枚）を、AI-OCR「AIよみと～る」で読み取りデータ化する仕組みを導入した。従来は職員1名が手作業で入力していた業務を自動化し、作業時間を削減した。</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>茨城県大子町、NTT東日本</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>記載なし（2019〜2020年頃と推定）</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>小規模町村における限定的だが定型的な紙帳票業務にAI-OCRを適用し、少人数体制でも運用可能な効率化を実現した点。LGWAN対応で住民情報を安全に扱える。</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>https://business.ntt-east.co.jp/case/daigotown-ai-ocr.html</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>大子町は別途「AI乗合タクシーたくまる」も運行</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="85" customHeight="1">
+      <c r="A48" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>AI-OCR・RPAと窓口サービスの連携実証（三鷹市）</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>東京都三鷹市がNTT東日本・アイネスと共同で、住民の各種申請書をAI-OCRでデータ化しRPAで基幹システムへ自動入力する実証実験を2019年6月に開始した。保育園入園受付の在職証明書スキャンにも展開し、読み取ったデータの分析結果をFAQ改善やチャットボットの回答精度向上にも活用している。</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>東京都三鷹市、NTT東日本、アイネス</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>2019年度</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>AI-OCR単体にとどまらず、電子申請・チャットボットと有機的に連携させ、データ活用まで一体で設計している点。</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.mitaka.lg.jp/c_press/080/080806.html</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="85" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>当別町 全庁的な生成AI導入</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>北海道当別町が2022年12月からChatGPTの検証を開始し、2023年7月の試験運用を経て同年10月に北海道内で初めて全庁的に生成AIを導入した。会議録の文字起こし・要約や広報文章の校正など幅広い業務に活用し、文字起こし・要約作業の時間を従来の4分の1に短縮した。</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>北海道当別町</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>2023年度</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>小規模自治体でありながら全庁導入に踏み切り、勉強会を30回以上重ねるなど職員のAIリテラシー育成を継続的に行っている運用体制。</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hokkaido-np.co.jp/article/913507/</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>2024年度からはRAGやMicrosoft 365 Copilotを使った追加検証「Go Beyond ChatGPT」も実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="85" customHeight="1">
+      <c r="A50" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>行政特化型生成AI「マサルくん」の導入（八雲町）</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>北海道八雲町の情報政策室が、公務員業務に特化した生成AIサービス「マサルくん」を導入し、文書作成やメール文案・校正など日常業務の効率化に活用している。デジタル田園都市国家構想の支援団体を通じ、自治体パートナーとして無償で利用できる仕組みを活用した。</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>北海道八雲町（情報政策室）</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>2024年度</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>全国627自治体・月27万回以上利用される特化型AIサービスを、少人数の情報担当部署が主体的に導入・運用している小規模自治体の事例。</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>https://www.town.yakumo.lg.jp/blog/information/index.php/2024/06/04/5302/</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="85" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>市民参加型AIチャットボット「ニャンぺい」実証実験（横須賀市）</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>神奈川県横須賀市が、OpenAIの「GPT-4o」を活用したお悩み相談チャットボット「ニャンぺい」を、あえて未完成の状態で公開する実証実験を2024年5月20日から約1カ月間実施した。市民から誤答や不適切な回答の報告を集めて改善に反映し、期間中に36,042件の対話が行われた。</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>神奈川県横須賀市</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>2024年度</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>完成品を提供するのではなく、市民参加によって「育てる」共創型のAI開発プロセスを採用し、実験結果を報告書として他自治体・企業にも公開共有した点。</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.yokosuka.kanagawa.jp/0835/nagekomi/20240520_soudanbot_nyanpei.html</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>横須賀市は2023年からChatGPTを全庁導入</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="85" customHeight="1">
+      <c r="A52" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>多言語通訳サービス「KOTOBAL」による窓口対応（川口市）</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>埼玉県川口市が、機械翻訳とオペレーター通訳を組み合わせたハイブリッド型多言語通訳サービス「KOTOBAL」を25台導入し、各窓口に配置した。人口の約7.1%（約4万3千人）を占める外国人住民、特にトルコ語しか話せないクルド系住民への対応強化を図った。</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>埼玉県川口市、コニカミノルタ</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>2023年度</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>従来利用していたAI通訳機では行政用語対応や音声認識精度が不十分だった課題を、32言語対応かつ複雑な相談時はビデオ通訳へ切替可能なハイブリッド型サービスで解決した点。</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>https://kotobal.konicaminolta.jp/case/10</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="85" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>生成AI福祉相談チャットボットの県域展開（千葉県）</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>千葉県が2025年2月27日から、生成AIを活用したチャットボット「いつでも福祉相談サポット」の運用を開始した。生活困窮・介護・子育てなど福祉分野の相談内容を丁寧に聞き取り整理した上で、県や市町村の担当窓口・相談支援機関を案内する仕組みを、県ホームページとLINEの両方で提供している。</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>千葉県（県内市町村と連携）</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>2025年度</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>単純なFAQ型応答ではなく生成AIが相談内容を丁寧に聞き取り整理する設計で、複合化・複雑化した相談にも対応でき、24時間365日いつでも利用できる県内市町村共同利用型の相談窓口モデルである点。</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pref.chiba.lg.jp/kenshidou/types/welfarechatbot.html</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>鎌ケ谷市・旭市・四街道市等、県内多数の市町村が案内</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="85" customHeight="1">
+      <c r="A54" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>鎌倉市 AIカメラ観光客混雑可視化実証実験</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>鎌倉高校前駅の踏切周辺など観光客が集中しオーバーツーリズムが課題となっているエリアにAI搭載カメラを設置し、来訪者数や混雑状況をリアルタイムに把握・可視化する社会実験を実施。取得データを混雑緩和策の検討や来訪者への情報発信に活用する。</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>鎌倉市</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>2025年度（実施期間2025年12月〜2026年3月）</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>アニメの聖地としてSNSで話題化した踏切という「点」的なスポット周辺の局所的混雑対策という、広域型ではなく狭小エリア特化型のオーバーツーリズム対策である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.kamakura.kanagawa.jp/kankou/aicamera.html</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="85" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>秩父市 三峰駐車場AIカメラ混雑可視化</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>市営三峰駐車場の出入口と周辺道路2箇所にAIカメラを設置し、駐車場・道路の混雑状況をリアルタイムに可視化。専用ポータル「VACAN Pages」やマップ型配信サイト「VACAN Maps」で発信するほか、2025年2月からは市内の道の駅2カ所にタッチ式デジタルサイネージも設置し、オーバーツーリズム対策としての情報提供を強化した。</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>秩父市、株式会社バカン</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>2024年2月（本格運用開始）〜2025年2月（サイネージ拡充）</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>山間観光地の駐車場と周辺道路渋滞を一体的にAIカメラで可視化し、デジタルサイネージという直接的な現地案内手段と組み合わせている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>https://corp.vacan.com/company/news/chichibucity.html</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="85" customHeight="1">
+      <c r="A56" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>函館山AIカメラ混雑状況配信システム</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>世界三大夜景として知られる函館山の山頂駅・山麓駅（ロープウェイ）周辺にAIカメラを設置し、混雑状況を「大混雑・混雑・やや混雑・空いています」の4段階でリアルタイムに可視化。JR函館駅など市内2カ所のデジタルサイネージおよび専用ウェブサイトで配信を開始した。</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>株式会社バカン、株式会社ネットリソースマネジメント（NRM）、ハコレコドットコム株式会社</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>2025年1月</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>観光名所単体（山・ロープウェイ）に特化した混雑可視化を、来訪前に確認できる駅構内サイネージと連動させ、来訪タイミングの分散を狙う設計が特徴。</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>https://corp.vacan.com/company/news/hakodaetyama.html</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="85" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>大阪観光局 多言語生成AIチャットボット導入</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>大阪観光局が運営する公式観光情報サイト「OSAKA-INFO」に、20言語以上に対応した生成AIチャットボット「Kotozna laMondo」を導入。700カ所を超える観光スポット情報を登録し、訪日外国人旅行者からの自然言語での多様な質問にスピーディーかつシームレスに回答する観光案内サービスを開始した。</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>一般財団法人大阪観光局、コトバウンク株式会社（Kotozna）</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>2023年10月</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>日本の自治体系観光サイトとして初めて多言語対応の生成AIチャットボットを本格導入した事例とされ、人気スポットへの集中を避け観光客を分散させる効果も期待されている。</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>https://www.jtbcorp.jp/jp/newsroom/2023/09/26_02_kotozna-lamondo.html</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="85" customHeight="1">
+      <c r="A58" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>大丸有エリア次世代型AIコンシェルジュ</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>大手町・丸の内・有楽町地区まちづくり協議会が構築・運営する都市OSと連携し、丸の内エリア公式マップアプリ「Oh MY Map!」に生成AI（LLM・RAG技術）を用いたAIコンシェルジュ機能を搭載。最新のエリアイベント情報やおすすめ飲食店情報などをリアルタイムに案内し、来街者の回遊性向上を図る。</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>三菱地所株式会社、株式会社NTTデータ、大手町・丸の内・有楽町地区まちづくり協議会</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>2025年1月</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>単一の観光地ではなく大規模オフィス街のエリアマネジメント団体が主体となり、独自に整備した都市OSのデータと連動させた点が特徴。</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>https://www.mec.co.jp/news/detail/2025/01/08_mec250108_ai%20concierge</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="85" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>富山市 AIカメラ人流データ計測プラットフォーム</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>富山駅周辺および中心商店街（総曲輪地区）に52台のAIカメラを設置し、都市OS上に人流観測プラットフォームを構築。年代・属性別の来訪者数や滞留状況を可視化し、商業者の新規出店に向けたマーケティング、イベントの効果検証、施設利用状況の分析などに活用している。</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>富山市</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>2023年4月</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>観光振興ではなく中心市街地の商業活性化・出店支援を明確な目的とし、市が整備した都市OSと連携させた大規模なAIカメラ網を構築している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.city.toyama.lg.jp/business/shokogyo/1010599/1012303.html</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="85" customHeight="1">
+      <c r="A60" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>京都市 AI渋滞予測モデルによる観光交通対策</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>観光客増加によるオーバーツーリズムに対応するため、AIによる画像解析データやETC2.0プローブデータを組み合わせて将来・当日の道路渋滞状況を予測するAI渋滞予測モデルを構築。予測結果を観光客・事業者向けに情報提供する実証実験を行い、市バスの混雑対策や人気エリアの混雑回避策と連動させている。</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>京都市</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>2019年開始〜2022年11月（AI渋滞予測実証実験）</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>観光案内アプリやチャットボットではなく、道路交通そのものの渋滞をAIで予測・提供する交通特化型の対策であり、公共交通事業者（市バス）の運行対策と直結させている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.travelvoice.jp/20200106-144107</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="85" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>上川町 AI×人流データ観光施策</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>層雲峡温泉などを抱えながらも「通過型の町」とされてきた上川町が、AIと人流データを組み合わせた分析により、リピーターやファミリー層など従来把握できていなかった来訪者層とその行動を可視化。得られた知見を、通過するだけの観光客を町内に滞在させるための新たな観光施策の検討に活用している。</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>北海道上川町、株式会社電通デジタル</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>2025年度</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>大都市や著名観光地ではなく人口数千人規模の小規模自治体が、「通過を滞在に変える」という明確な課題設定のもとAI人流分析を導入した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>https://www.dentsudigital.co.jp/knowledge-charge/cases/2026-0122-hokkaido-kamikawa</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="85" customHeight="1">
+      <c r="A62" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>板橋区 大山商店街AI人流データ活用</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>ハッピーロード大山商店街にAIカメラを設置し、AI交通量計測システムにより商店街の通行量（人流データ）を計測。中小企業庁の令和4年度IT導入補助金（複数社連携IT導入枠）を活用し、参加10店舗と連携してデータに基づく生産性向上の取り組みを2022年12月から試験運用した。</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>ハッピーロード大山商店街振興組合（東京都板橋区）</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>2022年度</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>個店単位ではなく商店街振興組合が主体となり、複数店舗が連携してAI人流データを共有・活用する「複数社連携型」の商店街DXである点が特徴。</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>https://www.chusho.meti.go.jp/shogyo/shogyo/jirei/07/pdf/03.pdf</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="85" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>AI橋梁簡易点検システムの導入（七尾市）</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>石川県七尾市は、管理橋梁の半数以上を占める5m未満の小規模橋梁を対象に、点検写真と部材・ひび割れ幅などの諸元データをAIに学習させて劣化要因・健全度を自動判定する「AI橋梁診断支援システム」を導入した。実証実験では健全度判定の正答率が80%台後半、劣化要因判定は90%超を記録し、その後の実運用でも高精度を維持している。点検単価は従来手法の約65%に低減できたと試算されている。</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>石川県七尾市（産学官共同研究、BIPROGY等が開発協力）</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>2019年頃に実証開始、2024年時点でも運用継続中</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>人手不足に悩む地方自治体でも定期点検を継続できるよう、小規模橋梁に特化して低コスト運用を実現した点が特徴。令和2年度インフラメンテナンス大賞優秀賞を受賞。</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hido.or.jp/14gyousei_backnumber/2021data/2104/2104AI_tenken_nanao_city.pdf</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>同種システム「Dr.Bridge」（BIPROGY）は他自治体にも展開中</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="85" customHeight="1">
+      <c r="A64" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>AIによる水道管路劣化診断（朝来市）</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県朝来市は、AIを用いて水道管路の劣化診断と管路台帳の不足項目補完を行い、市全域の水道事業を職員4名という少人数体制で効率的に運営している。診断結果を全庁共通の地理情報システム（GIS）に管路情報・劣化度として登録し、道路工事など他事業との調整にも活用している。</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>兵庫県朝来市</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>2023年前後</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>単なる劣化診断にとどまらず、全庁共通GISへの統合により上下水道部門以外の事業とも横断的に情報連携させている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>https://www.soumu.go.jp/denshijiti/digital_transformation_portal/case/dx3_32.html</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>総務省「自治体DX事例検索」に掲載された公式事例</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="85" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>AI漏水検知モバイル調査システムの実証（長崎市）</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>長崎市上下水道局は、漏水音データをAIで解析して漏水の有無を判定する新しいモバイル漏水調査システム「SuiDo_AI」の実証を2024年から開始した。従来は熟練技術者の経験に頼っていた漏水音の判断業務のうち約8割をAIに置き換えることを目指し、限られた人員でも調査可能な範囲を4倍以上に拡大することを目標としている。</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>長崎市上下水道局、wavelogy株式会社</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>熟練技術者の技能継承が難しくなっている水道事業の「音」による漏水判定業務にAIを応用し、属人化した技能をシステム化した点が特徴。</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000001.000133393.html</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="85" customHeight="1">
+      <c r="A66" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>衛星データ×AI漏水リスク管理「宇宙水道局」（全国展開）</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>宇宙ベンチャーの天地人は、衛星の観測データと地盤・地形などのビッグデータをAIで解析し、水道管の漏水リスクをマップ化するクラウドサービス「天地人コンパス 宇宙水道局」を全国の自治体・水道事業体向けに提供している。2023年4月のサービス開始から契約自治体数が急増し、2024年8月時点で契約自治体数が20を突破した。</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>株式会社天地人（JAXAベンチャー）、全国の水道事業者・自治体</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>2023年サービス開始</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>現地調査に頼らず衛星データとAIだけで広域の漏水リスクを可視化できるため、調査距離を大幅に削減でき、複数自治体で更新事業費の圧縮効果が報告されている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000143.000045963.html</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>サービスサイト https://suido.tenchijin.co.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="85" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>AIごみ収集ルート最適化「AI収集ナビ」実証（調布市）</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>東京都調布市は、Borzoi AI株式会社および電気通信大学と連携し、可燃・不燃ごみの収集車両を対象にAIで収集ルートを自動最適化する「AI収集ナビ」の実証実験を実施した。ルート最適化により走行距離や作業時間、燃料消費の削減を図り、収集業務の省人化・効率化を目指している。</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>東京都調布市、Borzoi AI株式会社、国立大学法人電気通信大学</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>2025年7月〜2026年3月</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>大学と自治体、AIスタートアップの産学官連携による実証で、地域課題（収集人員不足）解決を目的にした点が特徴。</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>https://prtimes.jp/main/html/rd/p/000000007.000139134.html</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="85" customHeight="1">
+      <c r="A68" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>AI潅水施肥スマート農業による震災復興（東松島市）</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>宮城県東松島市では、東日本大震災の被災跡地に開設された農産物栽培拠点に、日射・土壌センサーの情報をAIが解析し必要な水と肥料の量・タイミングを自動判断して点滴供給するAI潅水施肥システム「ゼロアグリ」を導入した。震災跡地の利活用と障がい者雇用の創出を同時に実現し、夏季の収量は導入前の2.5倍に向上した。</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>宮城県東松島市、KDDI株式会社、株式会社KDDIエボルバ</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>2016年頃導入、継続運用中</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>単なる農業効率化ではなく、被災地復興と障がい者雇用創出という地方創生的な社会課題解決を同時に達成した複合的な事例である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>https://biz.kddi.com/usecase/case_239/</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="85" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>AIスマートポールによる人流分析・観光情報配信（小田原市）</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>神奈川県小田原市は、NECと日本街路灯製造の協力により、街路灯にAIカメラ・センサー・サイネージ等を搭載した「スマートポール」を市内に設置した。人流データをAIで分析し、来訪者の属性や滞留状況に応じて観光情報や広告を発信するほか、小田原提灯を模したデザインで景観にも配慮している。</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>神奈川県小田原市、日本電気株式会社（NEC）、日本街路灯製造株式会社</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>2024年3月発表</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>インフラ設備（街路灯）にAI・IoTを実装し、防犯・防災機能に加えて観光振興・地域活性化の情報発信基盤としても活用している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>https://news.mynavi.jp/techplus/article/20240301-2896094/</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="85" customHeight="1">
+      <c r="A70" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>AI・IoTスマート道路灯による路面凍結警告実証（裾野市）</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>静岡県裾野市は、交通事故死者数ゼロを目標に、路面凍結が起こりやすい市道にAI・IoT連携のスマート道路灯を設置する実証実験を行った。車両の通過を検知すると路面に「凍結注意」の文字を投影し、ドライバーに視覚的に注意喚起する仕組みを構築した。</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>静岡県裾野市、NTT関連企業（OPEN HUB for Smart World共創プロジェクト）</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>2020年代前半</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>エネルギー・環境分野のインフラ（道路照明）を交通安全対策に転用し、住民の安全確保に直結させた具体的なユースケースである点が特徴。</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="inlineStr">
+        <is>
+          <t>https://openhub.ntt.com/project/8057.html</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="85" customHeight="1">
+      <c r="A71" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>AI脱炭素シナリオシミュレーターによる自治体政策支援（日立製作所）</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>日立製作所は、日立京大ラボが開発した未来シナリオ生成AI技術を応用し、自治体が2050年カーボンニュートラルに向けた長期ロードマップを検討できる「脱炭素シナリオシミュレーター」を開発した。地域のエネルギー・経済・環境データをもとに複数の脱炭素シナリオとその分岐点をAIが提示し、政策立案の意思決定を支援する。</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>株式会社日立製作所、日立京大ラボ、連携自治体</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>2021年開発、2026年5月に本格展開開始</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>個別インフラのAI点検ではなく、自治体全体の脱炭素政策の意思決定プロセス自体をAIでシミュレーション支援する上位レイヤーの事例である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hitachi.com/ja-jp/press/articles/2026/05/0528/</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="85" customHeight="1">
+      <c r="A72" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>水道データ×AIによる空き家発生予測（豊田市）</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>愛知県豊田市は、面積の8割を山間部が占め冬季の水道管凍結・破裂対応で空き家把握が課題となっていたことから、水道使用量データをAIで解析して空き家化を予兆検知するシステム「MiraiE.ai」を日本で初めて導入し実証実験を行った。令和4年度は空き家発生予測、令和5年度以降は再入居予測や成約価格シミュレーションにも対象を拡大した。</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>愛知県豊田市（上下水道局・建築相談課・情報戦略部門連携）、株式会社マイクロベース</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>2022年度実証開始、2023年度以降拡大</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>水道インフラデータという既存の行政データを空き家対策という全く別の政策課題に転用した部局横断型のデータ活用が特徴で、開発企業は本手法で特許を取得している。</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.vled.or.jp/2025/12/24/dxcase_toyota/</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>特になし</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>■ 海外事例（30件）</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n"/>
+      <c r="C73" s="3" t="n"/>
+      <c r="D73" s="3" t="n"/>
+      <c r="E73" s="3" t="n"/>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74" ht="85" customHeight="1">
+      <c r="A74" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>AIを活用したストリートデザインと市民参加（UrbanistAI）</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>夏季に自動車中心のストリートを人中心の公共空間へ転換する試みにおいて、市民や地域事業者を招いたワークショップを開催。UrbanistAIを用いて通りの写真から複数のデザイン案を共同生成し、建築設計事務所の具体設計の参考とした。</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>フィンランド（都市・自治体、UrbanistAI）</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>2023年度</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F74" s="5" t="inlineStr">
         <is>
           <t>市民が生成AIで自らストリートの未来像を描き、そのビジョンが実際の設計プロセスに反映される市民参加型デザイン手法が特徴。</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>https://note.com/taiyooo_0924/n/n625cb537b090</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H74" s="5" t="inlineStr">
         <is>
           <t>海外事例（フィンランド）</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>スマートシティ会津若松「都市OS」</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>自治体の既存システムを代替せず、複数分野に共通するニーズに応える基盤「都市OS」を開発。オプトイン方式のデータ活用と市民中心のICTを掲げ、食農・観光・防災・ヘルスケア・行政・決済等22サービスと連携。RPAやAIを活用した業務改革も推進。</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>会津若松市、アクセンチュア等</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2011年度〜（継続中）</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>住民の事前同意（オプトイン）に基づくデータ活用と、他自治体へも横展開可能な共通基盤である点が特徴。</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>https://robotstart.info/2023/03/20/aizu-aict-city-os.html</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>都市OSは全国複数都市に展開</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>柏の葉スマートシティ AIカメラによる人流分析・異常検知</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>柏の葉キャンパス駅周辺に国内最大規模となるエッジAIカメラ29台を設置し、AIによるリアルタイム画像分析で異常行動（転倒、うずくまり、凶器所持等）や不審な立ち入りの検知、歩行者の人流解析を実施。個人が特定できない形にデータを加工しプライバシーに配慮。</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>三井不動産、クリューシステムズ、UDCKタウンマネジメント</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2021年度〜</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>カメラ側で解析を完結するエッジAIにより、プライバシーに配慮しつつリアルタイムでの安心・安全なタウンマネジメントを実現する点が特徴。</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.mitsuifudosan.co.jp/corporate/news/2021/0921/</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>対象エリア：千葉県柏市 柏の葉キャンパス駅周辺</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>加古川市 AI搭載高度化見守りカメラ</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>市内約150カ所（累計約1,560台）にAI機能搭載の見守りカメラを設置。悲鳴等の異常音を検知し警告するI型と、危険運転検知・交通量や人流データの自動把握も行うII型を配備し、犯罪・交通事故の未然防止を図る。</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>加古川市</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2016年度〜（順次拡大、2023年度にAI高度化）</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>AIによる異常音・危険運転の自動検知と通報を組み合わせ、設置から約6年間で刑法犯認知件数が約4割減少する効果を上げた点が特徴。</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>https://kakogawa.keizai.biz/headline/2510</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2025年4月からは市民参加型「みまもりアプリ」も開始</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>つくばスーパーサイエンスシティ構想（オンデマンド型移動期日前投票所）</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>有権者がスマートフォンや電話で予約した日時に投票箱搭載車両が自宅前まで来訪するオンデマンド型移動期日前投票所の模擬実証を実施。立会人の役割の一部をロボットによる遠隔立会で代替する検証も実施。</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>つくば市、KDDI、スパイラル、東京海上日動</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2023年度（2024年1月実証）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>AI・ロボティクスとオンデマンド配車の組み合わせにより、移動困難者の投票参加を支援するまちづくり・行政DXの取り組みである点が特徴。</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.spiral-platform.co.jp/20240115/1479/</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>2024年秋の市長・市議選での一部実用化を目指す</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>AIオンデマンドバス「のるーと」</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>既存の地域振興バス路線を段階的にAIオンデマンド型のデマンド交通へ転換。利用者の予約に応じてAIが効率的な運行ルートをその都度生成し、過疎化・高齢化地域における移動手段を確保。</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>塩尻市（長野県）</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2021年度〜</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>全国有数の成功事例とされ、路線バスからAIオンデマンド交通への段階的な転換モデルを確立した点が特徴。</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>https://book.st-hakky.com/industry/ai-ondemand-transportation-innovation</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>同種の取り組みは玉野市（岡山県）、桑名市（三重県）、北本市（埼玉県）等でも展開</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="75" ht="85" customHeight="1">
+      <c r="A75" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>Virtual Singapore（バーチャル・シンガポール）</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>国土全域を対象に航空レーザー測量等で収集した25テラバイト超の地理空間データを基に、建物・道路・緑地から地下インフラまでを再現した世界初の国家規模デジタルツインを構築。都市計画のシミュレーションや防災・資源配分の最適化に活用。</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>シンガポール土地庁（SLA）、Bentley Systems</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>2014年度〜（2019年度に高度化）</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>国全体を対象とする国家規模のデジタルツインであり、AIやIoTと統合した継続的な都市シミュレーション基盤を目指す点が特徴。</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>https://en.wikipedia.org/wiki/Virtual_Singapore</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>海外事例（シンガポール）</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="90" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+    <row r="76" ht="85" customHeight="1">
+      <c r="A76" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>Helsinki 3D+（ヘルシンキ3Dシティモデル）</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>ヘルシンキ市全域を対象とした高精度3Dデジタルツインをオープンデータとして公開。市民参加のハッカソンやワークショップを通じたアイデア創出を継続的に行い、AI・IoTとの統合を進めている。</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>ヘルシンキ市（フィンランド）</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>2017年度〜（継続中）</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr">
         <is>
           <t>都市モデルを全面オープンデータ化し、市民が自由に活用・提案できる開かれた都市データ基盤である点が特徴。</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G76" s="5" t="inlineStr">
         <is>
           <t>https://news.build-app.jp/article/35961/</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>海外事例（フィンランド）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+    <row r="77" ht="85" customHeight="1">
+      <c r="A77" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>Sidewalk Labs「Quayside」計画の中止（トロント）</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>Alphabet傘下のSidewalk Labsが、トロントのウォーターフロント地区（約12エーカー）で自動運転車、AIによる交通流解析カメラ網、住宅への在室センサー設置など先端技術を統合したスマートシティ開発を計画したが、プライバシー・監視への住民の不信により2021年に計画を中止。</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>Sidewalk Labs（Alphabet／Google系）</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>2017年度計画発表、2021年度中止</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F77" s="5" t="inlineStr">
         <is>
           <t>AI活用まちづくりにおいて、技術先行でデータ活用への信頼醸成を欠くと計画自体が頓挫し得るという教訓を示す失敗事例である点が特徴。</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>https://www.technologyreview.com/2022/06/29/1054005/toronto-kill-the-smart-city/</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H77" s="5" t="inlineStr">
         <is>
           <t>海外事例（カナダ）／AI・データ活用の合意形成の重要性を示す反面教師的事例</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>渋谷区生成AIチャットボット</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>GPT-4o相当のモデルとRAG技術を組み合わせ、行政サービスの手続きや制度に関する住民からの問い合わせに自動で回答する生成AIチャットボットサービスを提供。ポータルサイトやLINEから利用可能。</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>渋谷区</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2025年度（2025年3月開始）</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>住民参加によるチューニング募集の仕組みを持つ「共創型AI」であり、開始2カ月で10万件超のQ&amp;A対応・解決率77%を達成した点が特徴。</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.city.shibuya.tokyo.jp/kusei/kocho/ai-chatbot/ai_chatbot.html</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>多言語対応・画像アップロード機能あり</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>仙台市新庁舎建替・東北大学青葉山新キャンパスにおけるAI活用実証</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>総務省「地域社会DX推進パッケージ事業（AI検証タイプ）」の一環として、建替工事現場においてAIを活用した実証実験を開始。7社によるコンソーシアムで現場業務の効率化・高度化を検証。</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>NTTドコモビジネス（代表）ほか7社コンソーシアム、仙台市、東北大学</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2025年度（2025年12月開始）</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>都市インフラ整備（庁舎・キャンパス建設）の現場そのものにAIを実装し、まちづくりの基盤整備プロセス自体を効率化する点が特徴。</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.ntt.com/about-us/area-info/article/20251205.html</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>総務省補正予算事業を活用</t>
+    <row r="78" ht="85" customHeight="1">
+      <c r="A78" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>カンザスシティ・スマートシティ構想</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>カンザスシティ市はシスコやスプリントと提携し、ストリートカー沿線2マイルに328基のWi-Fiアクセスポイント、178基のセンサー内蔵スマート街灯、25基の映像キオスクを設置した。街灯は交通量や空き駐車スペースを検知し、歩行者の動きに応じて信号や照明を動的に制御する。収集データはCisco Kinetic for CitiesとAWS上のデータレイクに集約され、都市インテリジェンス企業Xaqtが解析して交通・駐車・貧困対策等の政策判断に活用している。</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>カンザスシティ市（ミズーリ州）、Cisco、Sprint、Xaqt</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>2015年開始、2018年に第2フェーズへ移行</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>ストリートカー沿線を「実験室」と位置づけ、交通・Wi-Fi・街灯データを一元的なデータレイクに統合し、複数分野の政策に横断的に活用する統合型スマートシティの先行事例。</t>
+        </is>
+      </c>
+      <c r="G78" s="5" t="inlineStr">
+        <is>
+          <t>https://statetechmagazine.com/article/2018/04/kansas-city-streetcar-serves-laboratory-smart-city-thinking</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・ミズーリ州カンザスシティ</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="85" customHeight="1">
+      <c r="A79" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>サンディエゴ・スマート街灯プログラム</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>サンディエゴ市は2017年から市内に約3,200基のセンサー内蔵「スマート街灯」（カメラ・音声センサー付き）を設置し、交通・駐車管理に活用する計画を開始した。2020年にプライバシー懸念から一時停止されたが、2023年以降、市議会は透明性を高める条例（TRUST条例）とともに再稼働を承認し、Ubicquia社との契約のもと500基のカメラとFlock Safety社の自動車ナンバー認識（ALPR）技術を組み合わせて犯罪捜査に活用している。</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>サンディエゴ市、サンディエゴ市警察（SDPD）、Ubicquia社、Flock Safety社</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>2017年設置開始、2020年停止、2023〜2024年に再稼働</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>当初は交通・エネルギー効率化目的だったスマートインフラが、プライバシー論争を経て防犯・捜査目的のAI監視インフラへと性格を変えた、市民参加とガバナンスの緊張関係を示す事例。</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://cities-today.com/three-years-after-deactivation-smart-streetlights-are-back-in-san-diego/</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・カリフォルニア州サンディエゴ</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="85" customHeight="1">
+      <c r="A80" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>ピッツバーグのAI交通信号Surtrac</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>カーネギーメロン大学発のスタートアップが開発したAI交通信号システム「Surtrac」を導入し、各交差点の信号機がカメラ・センサーで接近車両の集団を検知し、リアルタイムに信号タイミングを自律的に最適化する。信号機同士がデータを共有し合うことで、単独最適化ではなく近隣交差点と連携した長期的な交通流予測・制御を実現している。</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>ピッツバーグ市、カーネギーメロン大学発スタートアップ（Surtrac／Rapid Flow Technologies）</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>2012年に9交差点で先行導入、その後50カ所から200カ所へ拡大</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>移動時間を最大26%、待ち時間を41%、排出ガスを21%削減したとされ、中央集権的な制御ではなく信号機同士が自律分散的に協調するAIアーキテクチャが特徴。</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
+        <is>
+          <t>https://www.smartcitiesdive.com/news/this-ai-traffic-system-in-pittsburgh-has-reduced-travel-time-by-25/447494/</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・ペンシルベニア州ピッツバーグ</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="85" customHeight="1">
+      <c r="A81" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>シカゴのArray of Thingsセンサー網</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>シカゴ大学・アルゴンヌ国立研究所などが主導し、市内のstreet furnitureに大気質・騒音・気温・人流などを計測するセンサーノードを多数設置する都市計測プロジェクト。プロジェクトの再設計により各ノードにNVIDIA製GPUを搭載し、エッジ側でAI画像解析を行うことで、人の行動や社会的相互作用など従来は人手観測でしか把握できなかった都市現象の計測を可能にした。</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>シカゴ市、シカゴ大学Computation Institute、アルゴンヌ国立研究所（米国科学財団助成）</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>2016年に全米初の都市展開開始、以降拡張・国際展開</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>クラウドではなくデバイス側（エッジ）でAI推論を行うことでプライバシーに配慮しつつ、データをオープンソースとして研究者・市民に無償公開する点が特徴。</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>https://www.anl.gov/article/chicago-becomes-first-city-to-launch-array-of-things-an-unprecedented-urban-sensing-project</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・イリノイ州シカゴ</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="85" customHeight="1">
+      <c r="A82" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>ボストンのAI活用「カーブラボ」</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>ボストン市新興技術局が2026年に開設した「Curb Lab」は、AIと公開データを用いて路肩（カーブ）の駐車規制・荷降ろし帯・自転車レーンなどの利用状況をリアルタイムにデジタル化する「Curb Data Management System」を構築した。市民・配達業者・都市計画者が検索可能な路肩規制マップも整備し、渋滞緩和や安全性向上、無駄な駐車探索の削減を目指している。</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>ボストン市新興技術局（Office of Emerging Technology）、米国運輸省SMART Grant</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>2026年開設</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>従来見落とされがちだった「路肩」という都市空間資源をAIでデジタルツイン化した初の取り組みとされ、米国内で「50 States, 50 Breakthroughs」に選出されるなど注目を集めた。</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>https://www.boston.gov/departments/emerging-technology/boston-curb-lab-using-ai-and-open-data-improve-curb-management</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・マサチューセッツ州ボストン</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="85" customHeight="1">
+      <c r="A83" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>バンクーバーのAI信号制御実証（グリーンライト）</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>カナダ・バンクーバー市はGoogleの「Project Green Light」に参加し、Googleマップの走行データをAIで分析して交通信号のタイミング変更を提案するパイロット事業を2025年7月から2027年末まで実施している。市はGoogle側の提案を受け取るが、実際に信号設定を変更するかどうかの最終判断権は市の交通技術者が保持する仕組み。</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>バンクーバー市（カナダ）、Google</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>2025年7月開始〜2027年末まで</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>市に費用負担のない形でAIによる信号最適化を試験導入し、AI提案と人間の最終意思決定を分離した「人間参加型（human-in-the-loop）」の運用モデルを採用している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>https://dailyhive.com/vancouver/vancouver-google-project-green-light-traffic-partnership</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>カナダ・ブリティッシュコロンビア州バンクーバー</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="85" customHeight="1">
+      <c r="A84" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr">
+        <is>
+          <t>NY市警のAI犯罪パターン分析Patternizr</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>ニューヨーク市警（NYPD）が内製した機械学習ツール「Patternizr」は、77管轄区にまたがる数十万件の犯罪記録の中から、同一犯による一連の犯行とみられる「パターン」を自動検出する。分析官が選んだ「シード」となる事件と過去の全事件を比較し類似度スコアを算出、類似度順にランキングして提示することで捜査官の初動分析を支援する。</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>ニューヨーク市警察（NYPD）</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>2016年12月運用開始（2019年に外部公表）</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>法執行機関で実運用された最初期の機械学習型犯罪分析ツールとされ、人種・性別・具体的地名などの機微属性を訓練データから除外してバイアス低減を図った点が特徴だが、専門家からは依然としてバイアスの懸念も指摘されている。</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>https://statescoop.com/how-the-nypd-is-using-machine-learning-to-spot-crime-patterns/</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・ニューヨーク市</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="85" customHeight="1">
+      <c r="A85" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>コロンバスのAI活用自動運転シャトルLinden LEAP</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>オハイオ州コロンバス市は連邦運輸省などから5,000万ドルの助成を得た「Smart Columbus」構想の一環として、交通事故多発地区であるリンデン地区で自動運転電気シャトル「Linden LEAP」を1年間の実証運行し、あわせて350〜500台の民間車両と750台の市・郡・交通機関の車両にリアルタイムの安全アラート技術を搭載、歩行者検知に応じて点灯するセンサー内蔵街灯も導入した。</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>コロンバス市（オハイオ州）、米国運輸省、Paul G. Allen Family Foundation</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>2016年助成獲得、2018年〜2020年頃に自動運転シャトル運行</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>富裕層向けが多い自動運転実証の中で、低所得・交通事故多発地区の住民の移動格差是正という「公平性（エクイティ）」を明確な目的に据えた点が特徴。</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>https://www.smartcitiesdive.com/news/smart-columbus-self-driving-shuttles-linden-LEAP/571905/</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ・オハイオ州コロンバス</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="85" customHeight="1">
+      <c r="A86" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Replicaによる都市計画AIプラットフォーム</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Google系列Sidewalk Labsからスピンオフしたスタートアップ「Replica」は、匿名化した携帯電話の位置情報や国勢調査データを機械学習で統合し、都市全域の人の移動を再現する「合成人口（シンセティック・ポピュレーション）」モデルを構築するプラットフォームを提供している。都市計画者はこのデータを用いてバス路線・自転車レーン・歩道整備など、実際の移動需要に基づいたインフラ計画やゾーニング判断を行うことができる。</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Replica社（Sidewalk Labsからのスピンオフ、独立企業として運営）</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>2016年開発開始、2019年独立、以降複数都市に展開</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>ポートランド・カンザスシティ・シカゴ・サクラメントなど複数の米国都市の交通局に採用され、位置情報データの出所の不透明さについて批判も受けている点が議論のポイント。</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="inlineStr">
+        <is>
+          <t>https://replicahq.com/</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>アメリカ各都市（本社サンフランシスコ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="85" customHeight="1">
+      <c r="A87" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>バルセロナのAIバス専用レーン取締り実証</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>バルセロナ市が主催する「Innova Lab Mobility」コンペティションで米Hayden AI社が採択され、バス車両に搭載したカメラとAI画像認識で、バス専用レーンやバス停の違法駐停車を自動検知する6か月間の実証実験を実施した。ナンバープレートや人物は記録せず、違反切符の発行も行わず、公共交通のダイヤ乱れの原因分析にデータを活用する仕組み。ヨーロッパでのバス車載型自動取締りシステムとしては最大規模の展開とされる。</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>バルセロナ市（Barcelona Innova Lab）、Hayden AI（米国企業）</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>2024年（コンペ選定・実証開始）</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>取締り・処罰目的ではなく、公共交通の運行効率改善のためのデータ収集に特化した点が特徴。米ニューヨーク市等での実績（バス速度5%向上、衝突20%減）を欧州都市に展開する事例。</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>https://www.hayden.ai/press/barcelona-launches-automated-bus-lane-and-bus-stop-enforcement-pilot-with-hayden-ai</t>
+        </is>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>スペイン・バルセロナ市</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="85" customHeight="1">
+      <c r="A88" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>アムステルダムのAI自動運転配車実証（metaCCAZE）</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>EU資金による「metaCCAZE」プロジェクトの一環として、アムステルダム市がリビングラボとして参加し、AIによる自動運転車両群のリアルタイム経路計画、自動EV充電、低排出交通管理など6つの新技術を実証している。市民・訪問者・事業者のニーズを反映させながら、電動・自動運転・コネクテッドモビリティへの転換を目指す。</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>アムステルダム市、欧州委員会（EU資金）、ERTICO（コーディネーター）ほか12か国44団体</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>2024年開始（実証は2024〜2025年）</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>アムステルダムに加えミュンヘン・リマソール（キプロス）・タンペレ（フィンランド）の4都市で同時多国間実証を行う点、AIを自動運転車両群の経路最適化に直接応用する点が特徴。総事業費約2,470万ユーロ。</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>https://www.metaccaze-project.eu/ai-and-smart-cities/</t>
+        </is>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>オランダ・アムステルダム市（他にドイツ・ミュンヘン、キプロス・リマソールも参加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="85" customHeight="1">
+      <c r="A89" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>ロンドン交通局（TfL）のAI交通信号制御</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>ロンドン交通局（TfL）が「London on the move」戦略の下、市内約3,500か所のバス優先信号を含む道路網全体でAIを活用した交通制御システム（Yutraffic Fusion）を2030年までに拡大導入する計画を発表。AIが渋滞発生箇所を予測し信号を自動調整するほか、VivaCity社製のAIセンサーが車・自転車・歩行者など交通モードを識別してリアルタイムでデータ収集する。</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>ロンドン交通局（TfL）、Yunex Traffic、VivaCity Labs</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>2018年（センサー試験開始）〜2030年（全面展開計画、2025年に戦略発表）</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>遅延を最大14%削減し10億ポンドの便益を見込むなど、大規模ネットワーク全体を対象とした定量目標を掲げている点が特徴。センサーは手動計測より最大98%高精度とされる。</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>https://www.traffictechnologytoday.com/news/traffic-management/tfl-deploys-ai-traffic-control-across-london-in-five-year-congestion-strategy.html</t>
+        </is>
+      </c>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>イギリス・ロンドン市</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="85" customHeight="1">
+      <c r="A90" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>コペンハーゲンのAI公共施設エネルギー最適化</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>コペンハーゲン市のイノベーション部門「Copenhagen Solutions Lab」が主導する「AIエネルギープロジェクト」により、市有建物の暖房・電力使用をAIで分析・最適化し、エネルギー消費とCO2排出を削減する取り組みを実施。市が2025年までに世界初のカーボンニュートラル首都を目指す戦略の一部として位置づけられている。</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>コペンハーゲン市（Copenhagen Solutions Lab）</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>2020年代前半（Copenhagen Solutions Lab主導、2025年目標に向けた取り組み）</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>交通やセンサーではなく「公共建築物のエネルギー管理」にAIを特化させ、行政コスト（光熱費）削減と気候目標達成を同時に狙う点が特徴。</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>https://mayorsofeurope.eu/ai-the-city/copenhagen-how-ai-is-rewriting-the-rules-of-urban-energy/</t>
+        </is>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>デンマーク・コペンハーゲン市</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="85" customHeight="1">
+      <c r="A91" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>ハンブルクほか独3都市の都市デジタルツイン(CUT)</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>ドイツ連邦政府の支援を受け、ハンブルク・ライプツィヒ・ミュンヘンの3都市が共同で「Connected Urban Twins（CUT）」プロジェクトを実施。建物や道路、行政手続き・市民参加・交通制御などをAI、データサイエンス、IoTを用いてデジタルツイン化し、都市計画のシミュレーションと意思決定支援に活用している。</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>ドイツ連邦政府、ハンブルク市、ライプツィヒ市、ミュンヘン市</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>2021年開始〜2025年末まで</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>単独都市でなく3都市が共通のデータプラットフォーム基盤を共同開発する点、総額約3,200万ユーロ（連邦2,100万ユーロ＋3市1,100万ユーロ）の公的資金規模が特徴。</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>https://hamburg-business.com/en/news/smart-city-german-government-funding-digital-twins-project</t>
+        </is>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>ドイツ・ハンブルク、ライプツィヒ、ミュンヘン各市</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="85" customHeight="1">
+      <c r="A92" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>エストニアの音声AI行政サービス「Bürokratt」</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>エストニア情報システム庁（RIA）が国家AI戦略「KrattAI」に基づき、音声対話型のAI仮想アシスタント「Bürokratt」を開発・運用。市民が日常的なエストニア語で行政サービスに関する問い合わせを行うと、複数の公共・民間サービスを横断する単一の窓口として案内し、対応困難な場合は人的窓口へ引き継ぐ仕組み。</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>エストニア情報システム庁（RIA）、エストニア経済通信省</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>2019年（KrattAI国家戦略採択）〜継続運用中</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>都市単体でなく国全体の行政サービスをAIで横断統合する「デジタル国家」型アプローチであり、官民のAIエージェント・ボットを単一チャネルに束ねる相互運用ネットワーク構想である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>https://e-estonia.com/estonias-new-virtual-assistant-aims-to-rewrite-the-way-people-interact-with-public-services/</t>
+        </is>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>エストニア（タリン含む国全体）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="85" customHeight="1">
+      <c r="A93" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>EU「気候中立・スマート都市ミッション」AI都市計画公募</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>欧州委員会はHorizon Europeの一環として「100の気候中立・スマート都市2030年ミッション」を推進し、加盟27か国から100都市・関連国から12都市の計112都市を選定。2025年には生成AIを含むAIを活用したデジタルツインを都市計画・政策決定に統合するための公募（総額2,400万ユーロ、1件あたり約600万ユーロ）を実施し、異なる加盟国の3都市以上が共同参加することを要件とした。</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>欧州委員会（欧州気候・インフラ・環境庁CINEA）、参加112都市</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>2022年（都市選定）、2025年（AI公募開始、締切2025年9月）</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>単一都市の事例でなくEU全体の資金制度として、複数都市共同でのAI駆動デジタルツイン開発を要件化している点、生成AI活用も明示的に対象としている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>https://cinea.ec.europa.eu/funding-opportunities/calls-proposals/horizon-europe-eur-855-million-available-under-climate-neutral-and-smart-cities-eu-mission_en</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>EU全域（欧州委員会主導、112都市が対象）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="85" customHeight="1">
+      <c r="A94" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>ユトレヒトの気候適応デジタルツイン（Urban ReLeaf）</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>オランダ・ユトレヒト市はHorizon Europe資金による「Urban ReLeaf」プロジェクトを通じ、市内4地区の住民が測定した気温・湿度・ヒートアイランドのデータを市のデジタルツイン（3Dモデル）に統合。これにより市初となる包括的なヒートマップを作成し、緑地整備や冷却インフラ設置の優先順位付けなど気候適応計画に活用している。</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>ユトレヒト市、Urban ReLeafコンソーシアム（欧州6都市参加、Horizon Europe資金）</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>2023年頃開始〜2025年（成果報告）</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>市民参加型の環境モニタリング（シチズンサイエンス）データをAI・デジタルツインに直接統合し、インフラ意思決定を30%高速化、12種類の気候適応シナリオを可視化するなど定量成果を示している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>https://urbanreleaf.eu/2025/04/09/utrechts-digital-twin-advancing-data-driven-urban-planning/</t>
+        </is>
+      </c>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>オランダ・ユトレヒト市</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="85" customHeight="1">
+      <c r="A95" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>杭州City Brain（城市大脑）AI交通制御</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>アリババクラウドが杭州市と共同で、交差点カメラ映像・GPSデータ・信号機情報をAIでリアルタイム統合分析し、市内1,000以上の信号を自動制御するシステムを構築した。2016年に杭州で試験導入され、2018年には「City Brain 2.0」として420km・1,300以上の信号・多数の監視カメラをカバーする規模に拡大した。渋滞順位を全国5位から57位まで改善し、救急車の現場到着時間を半減させた。</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>アリババクラウド（Alibaba Cloud）、杭州市政府</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>2016年〜（2018年に2.0へ拡大）</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>民間IT企業（アリババ）が主導し都市全体のリアルタイムデータを「都市の脳」として一元的にAI処理する点が特徴で、その後15以上の中国国内都市やクアラルンプールにも輸出された。</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="inlineStr">
+        <is>
+          <t>https://www.cnn.com/2019/01/15/tech/alibaba-city-brain-hangzhou</t>
+        </is>
+      </c>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>中国・浙江省杭州市</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="85" customHeight="1">
+      <c r="A96" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>深圳「都市交通ブレイン」AI取締システム</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>深圳市公安局交通警察支局とファーウェイが共同で、ビデオクラウド・ビッグデータ・AIを組み合わせた「City-wide Traffic Brain」を構築し、信号設置済みの全交差点をリアルタイム監視する体制を整えた。AI画像解析により交通違反を自動検出するオフサイト取締システムを導入し、違反検知精度は95%に達した。ビッグデータによる車線再編で道路容量も約8%向上した。</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>深圳市公安局交通警察支局、ファーウェイ（Huawei）</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>2010年代後半〜</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="inlineStr">
+        <is>
+          <t>単なる信号制御にとどまらず、AI画像認識による違反自動摘発と5G活用の将来計画まで含む「取締り」重視型のスマート交通システムである点が特徴。</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="inlineStr">
+        <is>
+          <t>https://e.huawei.com/topic/leading-new-ict-jp/shenzhen-traffic-police.html</t>
+        </is>
+      </c>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>中国・広東省深圳市</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="85" customHeight="1">
+      <c r="A97" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>松島（ソンド）国際業務地区ユビキタスシティ</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>仁川市沖の埋立地に建設された総事業費350億ドル規模の都市開発で、Gale International・POSCO E&amp;C・仁川市の共同事業として2001年に始動した。市内の建物・交通・エネルギー消費をセンサーとネットワークで統合管理する「ユビキタスシティ（U-City）」構想を具現化し、個人単位で市民と都市がインタラクションできる仕組みを目指した。</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Gale International、POSCO E&amp;C、仁川広域市</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>2001年〜（現在も開発継続、完成度約86%）</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>AIやセンサーを活用した都市OSを都市計画段階から組み込んだ世界初の大規模グリーンフィールド型スマートシティである点が特徴。ただし人口増加の伸び悩みなど課題も指摘されている。</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Songdo</t>
+        </is>
+      </c>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>韓国・仁川広域市松島（ソンド）地区</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="85" customHeight="1">
+      <c r="A98" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>世宗5-1生活圏 国家試範スマートシティ</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>韓国政府（国土交通省）が世宗市の未開発エリア（幸福都市の未湖川・錦江合流部）を対象に、第4次産業革命関連技術を実証する「国家試範都市」事業として推進している。モビリティ・ヘルスケア・教育・雇用・エネルギー・環境・ガバナンス・文化・生活安全など7分野の革新要素を組み込んだ都市空間を計画・整備する。</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>大韓民国国土交通省、世宗市、韓国土地住宅公社（LH）等</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>2018年計画開始〜（順次整備中）</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>既存市街地の改修ではなく更地から未来型スマートシティを一から設計・実証する「リビングラボ」型アプローチが特徴で、釜山エコデルタシティと並ぶ韓国の2大国家試範都市の一つ。</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="inlineStr">
+        <is>
+          <t>https://smartcity.go.kr/en/2022/08/25/designing-tomorrow-sejong-national-pilot-smart-city/</t>
+        </is>
+      </c>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>韓国・世宗特別自治市5-1生活圏</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="85" customHeight="1">
+      <c r="A99" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>インド・スマートシティミッションのICCC統合司令センター</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>インド政府の「スマートシティミッション」の一環として、全国100都市すべてにAI・ビッグデータ解析を活用した統合指令管制センター（ICCC）が運用開始された。ICCCは犯罪追跡、治安・防犯、交通管理、廃棄物管理、上水道管理など多様な都市サービスをAIによる予測・自動化・アラートで一元的に監視・意思決定支援する「都市の頭脳」として機能する。</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>インド住宅・都市問題省（MoHUA）、各都市のスマートシティ特別目的会社（SPV）</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>2015年ミッション開始、2023年頃までに全100都市で稼働完了</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>交通・防犯だけでなくCOVID-19対応の「戦時司令室」としても転用されるなど、単一分野ではなく都市運営全般を横断的にAIで統合管理する国家規模の取り組みである点が特徴。</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="inlineStr">
+        <is>
+          <t>https://www.pib.gov.in/PressReleaseIframePage.aspx?PRID=1907135</t>
+        </is>
+      </c>
+      <c r="H99" s="5" t="inlineStr">
+        <is>
+          <t>インド全国100都市（国家プロジェクト）</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="85" customHeight="1">
+      <c r="A100" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>ドバイRTA「AI戦略2030」交通AI改革</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>ドバイ首長国道路交通庁（RTA）が「Dubai AI Week 2025」で発表した「AI戦略2030」で、今後5年間で81件のAIプロジェクト・施策を実施すると発表した。市民満足度、モビリティ、交通管理、免許発行、組織運営、資産管理の6つの柱にわたり、AIによる信号最適化や歩行者移動支援などで移動時間を20〜30%短縮することを目指す。</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>ドバイ道路交通庁（RTA）</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>2025年発表（2030年までの実行計画）</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="inlineStr">
+        <is>
+          <t>単一システムではなく交通・免許・組織運営まで含む行政全体をカバーする包括的AI戦略である点、UAE国家AI戦略2031と連動している点が特徴。</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="inlineStr">
+        <is>
+          <t>https://www.rta.ae/wps/portal/rta/ae/home/news-and-media/all-news/NewsDetails/launching-ai-strategy-2030-featuring-81-projects-and-initiatives</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>アラブ首長国連邦（UAE）・ドバイ</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="85" customHeight="1">
+      <c r="A101" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>NEOM「THE LINE」AIファーストシティ構想</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>サウジアラビア政府が推進する総事業費5,000億ドル規模の巨大都市計画「NEOM」の中核プロジェクトとして、全長170km・高さ500m・幅わずか200mの直線都市「THE LINE」を計画した。都市のあらゆるセンサー・データをAIが一元的に集約・解析する中央プラットフォームにより都市機能を制御する、設計段階から「AIファースト」を掲げる世界初のコグニティブ・スマートシティを標榜している。</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>サウジアラビア公共投資基金（PIF）、NEOM社</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>2017年構想発表〜（2026年時点で本体工事は2030年以降に延期）</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>車道を排除し全機能を垂直・直線状に配置する前例のない都市構造に加え、都市OS全体をAIで統合設計する野心的な構想である一方、資金・現実性の課題から工事延期が報じられている。</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="inlineStr">
+        <is>
+          <t>https://themiddleeastinsider.com/2026/01/16/neom-reveals-smart-city-technology-infrastructure/</t>
+        </is>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>サウジアラビア・タブーク州（紅海沿岸）</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="85" customHeight="1">
+      <c r="A102" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>ブリスベン市AI信号制御パイロット事業</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>オーストラリア・ブリスベン市議会がオーストラリア初となるAI支援型信号制御システムを導入し、Logan Road沿い22交差点とKelvin Grove Road沿い15交差点の計37交差点で6か月間のパイロット事業を実施した。1950年代から続く定周期式の信号制御に代わり、交通量と待ち行列の長さをAIがリアルタイムに解析して最適な信号切替パターンを算出する。</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>ブリスベン市議会（Brisbane City Council）</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>2026年（パイロット開始）</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="inlineStr">
+        <is>
+          <t>総額1,500万豪ドルを投じた実証実験で、平均走行時間を最大15%短縮、追突事故を12%削減することを目標とする、オーストラリア初のAI信号制御の実地導入事例である点が特徴。</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="inlineStr">
+        <is>
+          <t>https://www.abc.net.au/news/2026-09-10/brisbane-traffic-light-signalling-artificial-intelligence-pilot/107136566</t>
+        </is>
+      </c>
+      <c r="H102" s="5" t="inlineStr">
+        <is>
+          <t>オーストラリア・クイーンズランド州ブリスベン市</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="85" customHeight="1">
+      <c r="A103" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>キガリ「CleanKigali」AI都市衛生管理プラットフォーム</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>ルワンダの首都キガリ市は、ICT省・キガリ市・国際協力機関等と連携し、AIを活用した都市清掃・衛生管理デジタルプラットフォーム「CleanKigali」を構築した。ゴミ収集・清掃状況をAIとセンサーネットワークでモニタリングし、市民からの通報や大気質データも統合して都市の衛生・持続可能性向上を図っている。</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>ルワンダ・イノベーションICT省、キガリ市</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>2020年代前半〜継続中</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>アフリカの新興都市において、AIとセンサー網を都市清掃・衛生管理という基礎インフラ分野に応用し、市民参加の通報機能と組み合わせている点が特徴。</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="inlineStr">
+        <is>
+          <t>https://cleankigali.kigalicity.gov.rw/</t>
+        </is>
+      </c>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>アフリカ・ルワンダ共和国キガリ市</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H16"/>
+  <autoFilter ref="A1:H103"/>
+  <mergeCells count="2">
+    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>